--- a/document/교육일정.xlsx
+++ b/document/교육일정.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
   <si>
     <t>교육주제</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -221,6 +221,10 @@
   </si>
   <si>
     <t>React.js, 스프링 부트, AWS로 배우는 웹 개발 101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>클라우드 기반 데이터 분석</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -895,7 +899,7 @@
         <v>45</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>33</v>
@@ -906,7 +910,7 @@
         <v>28</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" s="10">
         <v>50</v>
